--- a/data/trans_orig/P1435-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Edad-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61225</t>
+          <t>63461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93537</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61225</t>
+          <t>63461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93537</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373952</t>
+          <t>374160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>406264</t>
+          <t>404028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373952</t>
+          <t>374160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>406264</t>
+          <t>404028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>111759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76663</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>111759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>512989</t>
+          <t>513735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>548831</t>
+          <t>549710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512989</t>
+          <t>513735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>548831</t>
+          <t>549710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77422</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77422</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612322</t>
+          <t>612542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642916</t>
+          <t>641554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612322</t>
+          <t>612542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642916</t>
+          <t>641554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487329</t>
+          <t>487842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503969</t>
+          <t>504341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>487329</t>
+          <t>487842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503969</t>
+          <t>504341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396024</t>
+          <t>395908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403194</t>
+          <t>403986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396024</t>
+          <t>395908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>403194</t>
+          <t>403986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>335042</t>
+          <t>334783</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>342060</t>
+          <t>342050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335042</t>
+          <t>334783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342060</t>
+          <t>342050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>325639</t>
+          <t>326292</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325639</t>
+          <t>326292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58752</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58752</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371478</t>
+          <t>370715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396226</t>
+          <t>396621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>371478</t>
+          <t>370715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>396226</t>
+          <t>396621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25568</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49729</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25568</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49729</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560526</t>
+          <t>560624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584687</t>
+          <t>584217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>560526</t>
+          <t>560624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>584687</t>
+          <t>584217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>62651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>62651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>649524</t>
+          <t>646923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>676449</t>
+          <t>675678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649524</t>
+          <t>646923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676449</t>
+          <t>675678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596592</t>
+          <t>595238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609843</t>
+          <t>609824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596592</t>
+          <t>595238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609843</t>
+          <t>609824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363186</t>
+          <t>363626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381469</t>
+          <t>381966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363186</t>
+          <t>363626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381469</t>
+          <t>381966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>530354</t>
+          <t>530086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>549345</t>
+          <t>548698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>530354</t>
+          <t>530086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549345</t>
+          <t>548698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640597</t>
+          <t>640735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655468</t>
+          <t>654568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640597</t>
+          <t>640735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655468</t>
+          <t>654568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631213</t>
+          <t>631468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643978</t>
+          <t>644232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631213</t>
+          <t>631468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643978</t>
+          <t>644232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6902,32 +6902,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6937,32 +6937,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -6980,32 +6980,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>282792</t>
+          <t>321621</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264794</t>
+          <t>301262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>294984</t>
+          <t>336327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7015,32 +7015,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>282792</t>
+          <t>321621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264794</t>
+          <t>301262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294984</t>
+          <t>336327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>129788</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280695</t>
+          <t>83040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>129788</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280695</t>
+          <t>83040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>380392</t>
+          <t>432014</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229485</t>
+          <t>415429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445415</t>
+          <t>447877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>380392</t>
+          <t>432014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229485</t>
+          <t>415429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445415</t>
+          <t>447877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510180</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7378,32 +7378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>60238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>88458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>60238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>88458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -7456,32 +7456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>475257</t>
+          <t>545078</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>529796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>486771</t>
+          <t>558016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7491,32 +7491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>475257</t>
+          <t>545078</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>529796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>486771</t>
+          <t>558016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -7534,17 +7534,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>538632</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7616,32 +7616,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>36105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51682</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>36105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51682</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>670082</t>
+          <t>689069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>659450</t>
+          <t>678102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>679472</t>
+          <t>699037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7729,32 +7729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>670082</t>
+          <t>689069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659450</t>
+          <t>678102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679472</t>
+          <t>699037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711132</t>
+          <t>735142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7854,22 +7854,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7889,22 +7889,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -7932,27 +7932,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>542523</t>
+          <t>604427</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538819</t>
+          <t>600924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544139</t>
+          <t>606086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7967,27 +7967,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>542523</t>
+          <t>604427</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>538819</t>
+          <t>600924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544139</t>
+          <t>606086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607786</t>
+          <t>438506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8521,17 +8521,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425246</t>
+          <t>464002</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8603,32 +8603,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8681,32 +8681,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
